--- a/api/src/main/resources/importaciones/Compra Impuestos.xlsx
+++ b/api/src/main/resources/importaciones/Compra Impuestos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ismael\Documents\calero-app-desktop\api\src\main\resources\importaciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1280D923-6E63-4D84-8508-BFDA2CF5C6BA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A684F566-DE01-41FB-A3E3-868514AF61C9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" xr2:uid="{D37E80EC-E639-4DD6-860C-2105308D7D22}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1478" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1560" uniqueCount="216">
   <si>
     <t>ProvRUCCedPas</t>
   </si>
@@ -36,9 +36,6 @@
     <t>ProvNombre</t>
   </si>
   <si>
-    <t>ProvTipdocu</t>
-  </si>
-  <si>
     <t>Relacionada</t>
   </si>
   <si>
@@ -673,6 +670,12 @@
   </si>
   <si>
     <t>JUAN ALDO</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>Tipo Id Prov</t>
   </si>
 </sst>
 </file>
@@ -1089,8 +1092,9 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" style="1" customWidth="1"/>
+    <col min="3" max="3" width="20.42578125" style="1" customWidth="1"/>
     <col min="4" max="4" width="12.7109375" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" style="1"/>
+    <col min="5" max="5" width="24.140625" style="1" customWidth="1"/>
     <col min="6" max="6" width="15.7109375" style="1" customWidth="1"/>
     <col min="7" max="8" width="11.42578125" style="21"/>
     <col min="9" max="9" width="12" style="1" customWidth="1"/>
@@ -2322,203 +2326,203 @@
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="H1" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="21" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="T1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="U1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="V1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="W1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="4" t="s">
+      <c r="X1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="5" t="s">
+      <c r="Z1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="s">
+      <c r="AH1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>33</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>34</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>35</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>36</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>38</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>39</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>40</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>41</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AR1" s="1" t="s">
+      <c r="AS1" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="AS1" s="3" t="s">
+      <c r="AT1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AT1" s="1" t="s">
+      <c r="AU1" t="s">
         <v>45</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>47</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>48</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>49</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="BA1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="BB1" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="BB1" s="6" t="s">
+      <c r="BC1" t="s">
         <v>53</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BD1" t="s">
         <v>54</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="BE1" s="7" t="s">
+      <c r="BF1" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="BF1" s="8" t="s">
+      <c r="BG1" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="BG1" s="8" t="s">
+      <c r="BH1" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="BH1" s="8" t="s">
+      <c r="BI1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="BI1" s="1" t="s">
+      <c r="BJ1" t="s">
         <v>60</v>
-      </c>
-      <c r="BJ1" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:62" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="B2" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2" s="10">
-        <v>1</v>
+      <c r="C2" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D2" s="10" t="b">
         <v>1</v>
       </c>
       <c r="E2" s="9"/>
       <c r="F2" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G2" s="22">
         <v>45387</v>
@@ -2527,28 +2531,28 @@
         <v>45387</v>
       </c>
       <c r="I2" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="J2" s="9" t="s">
         <v>65</v>
-      </c>
-      <c r="J2" s="9" t="s">
-        <v>66</v>
       </c>
       <c r="K2" s="10">
         <v>8057</v>
       </c>
       <c r="L2" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="M2" s="22">
         <v>45721</v>
       </c>
       <c r="N2" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="O2" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="O2" s="10" t="s">
+      <c r="P2" s="10" t="s">
         <v>69</v>
-      </c>
-      <c r="P2" s="10" t="s">
-        <v>70</v>
       </c>
       <c r="R2" s="10">
         <v>1000</v>
@@ -2561,7 +2565,7 @@
         <v>150</v>
       </c>
       <c r="AG2" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AH2" s="10">
         <f>Q2+R2+U2+X2+Y2</f>
@@ -2575,49 +2579,49 @@
         <v>27.5</v>
       </c>
       <c r="AP2" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ2" s="10">
         <v>12327</v>
       </c>
       <c r="AR2" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS2" s="11">
         <v>45387</v>
       </c>
       <c r="AT2" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU2" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW2" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX2" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY2" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="AU2" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW2" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX2" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY2" s="10" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ2" s="12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="BA2" s="9"/>
       <c r="BI2" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:62" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="B3" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="B3" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C3" s="10">
-        <v>1</v>
+      <c r="C3" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D3" s="10" t="b">
         <v>0</v>
@@ -2631,28 +2635,28 @@
         <v>45389</v>
       </c>
       <c r="I3" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="J3" s="9" t="s">
         <v>65</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>66</v>
       </c>
       <c r="K3" s="10">
         <v>1284</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M3" s="22">
         <v>45738</v>
       </c>
       <c r="N3" s="23" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O3" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="P3" s="10" t="s">
         <v>79</v>
-      </c>
-      <c r="P3" s="10" t="s">
-        <v>80</v>
       </c>
       <c r="Q3" s="10">
         <v>980</v>
@@ -2668,7 +2672,7 @@
         <v>0</v>
       </c>
       <c r="AG3" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AH3" s="10">
         <f t="shared" ref="AH3:AH64" si="0">Q3+R3+U3+X3+Y3</f>
@@ -2681,49 +2685,49 @@
         <v>19.600000000000001</v>
       </c>
       <c r="AP3" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ3" s="10">
         <v>12328</v>
       </c>
       <c r="AR3" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS3" s="11">
         <v>45389</v>
       </c>
       <c r="AT3" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU3" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW3" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX3" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY3" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="AU3" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW3" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX3" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY3" s="10" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ3" s="12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="BA3" s="9"/>
       <c r="BI3" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:62" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="B4" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="C4" s="10">
-        <v>1</v>
+      <c r="C4" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D4" s="10" t="b">
         <v>0</v>
@@ -2737,28 +2741,28 @@
         <v>45392</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K4" s="10">
         <v>507</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M4" s="22">
         <v>45607</v>
       </c>
       <c r="N4" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O4" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P4" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q4" s="10">
         <v>0</v>
@@ -2774,7 +2778,7 @@
         <v>2.2599999999999998</v>
       </c>
       <c r="AG4" s="12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AH4" s="10">
         <f t="shared" si="0"/>
@@ -2787,42 +2791,42 @@
         <v>0</v>
       </c>
       <c r="AP4" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AR4" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AS4" s="11"/>
       <c r="AT4" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU4" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW4" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX4" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY4" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="AU4" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW4" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX4" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY4" s="10" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ4" s="12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="BA4" s="9"/>
       <c r="BI4" s="9"/>
     </row>
     <row r="5" spans="1:62" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="B5" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="C5" s="10">
-        <v>1</v>
+      <c r="C5" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D5" s="10" t="b">
         <v>0</v>
@@ -2836,28 +2840,28 @@
         <v>45393</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K5" s="10">
         <v>3072</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M5" s="22">
         <v>45529</v>
       </c>
       <c r="N5" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O5" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P5" s="14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q5" s="10">
         <v>0</v>
@@ -2873,7 +2877,7 @@
         <v>154.69999999999999</v>
       </c>
       <c r="AG5" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AH5" s="10">
         <f t="shared" si="0"/>
@@ -2886,49 +2890,49 @@
         <v>10.31</v>
       </c>
       <c r="AP5" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ5" s="10">
         <v>12331</v>
       </c>
       <c r="AR5" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS5" s="11">
         <v>45393</v>
       </c>
       <c r="AT5" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU5" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW5" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX5" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY5" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="AU5" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW5" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX5" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY5" s="10" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ5" s="12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="BA5" s="9"/>
       <c r="BI5" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:62" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="B6" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="C6" s="10">
-        <v>1</v>
+      <c r="C6" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D6" s="10" t="b">
         <v>0</v>
@@ -2942,28 +2946,28 @@
         <v>45399</v>
       </c>
       <c r="I6" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="J6" s="9" t="s">
         <v>65</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>66</v>
       </c>
       <c r="K6" s="10">
         <v>127</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M6" s="22">
         <v>45577</v>
       </c>
       <c r="N6" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O6" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P6" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q6" s="10">
         <v>0</v>
@@ -2982,7 +2986,7 @@
         <v>1334.26</v>
       </c>
       <c r="AG6" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH6" s="10">
         <f t="shared" si="0"/>
@@ -2996,49 +3000,49 @@
         <v>648.6</v>
       </c>
       <c r="AP6" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ6" s="10">
         <v>12329</v>
       </c>
       <c r="AR6" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS6" s="11">
         <v>45399</v>
       </c>
       <c r="AT6" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU6" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW6" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX6" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY6" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="AU6" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW6" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX6" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY6" s="10" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ6" s="12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="BA6" s="9"/>
       <c r="BI6" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:62" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="C7" s="10">
-        <v>1</v>
+      <c r="C7" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D7" s="10" t="b">
         <v>0</v>
@@ -3052,28 +3056,28 @@
         <v>45399</v>
       </c>
       <c r="I7" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="J7" s="9" t="s">
         <v>65</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>66</v>
       </c>
       <c r="K7" s="10">
         <v>1683</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M7" s="22">
         <v>45741</v>
       </c>
       <c r="N7" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O7" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P7" s="14" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Q7" s="10">
         <v>500</v>
@@ -3089,7 +3093,7 @@
         <v>0</v>
       </c>
       <c r="AG7" s="9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AH7" s="10">
         <v>300</v>
@@ -3102,47 +3106,47 @@
         <v>6</v>
       </c>
       <c r="AP7" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ7" s="10">
         <v>12333</v>
       </c>
       <c r="AR7" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS7" s="11">
         <v>45399</v>
       </c>
       <c r="AT7" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU7" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW7" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX7" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY7" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="AU7" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW7" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX7" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY7" s="10" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ7" s="12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="BA7" s="9"/>
       <c r="BI7" s="9"/>
     </row>
     <row r="8" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B8" t="s">
         <v>102</v>
       </c>
-      <c r="B8" t="s">
-        <v>103</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
+      <c r="C8" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D8" t="b">
         <v>0</v>
@@ -3154,28 +3158,28 @@
         <v>45399</v>
       </c>
       <c r="I8" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J8" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="K8">
         <v>17978</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M8" s="21">
         <v>45773</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O8" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P8" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -3194,7 +3198,7 @@
         <v>16.04</v>
       </c>
       <c r="AG8" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH8">
         <f t="shared" si="0"/>
@@ -3208,48 +3212,48 @@
         <v>7.8</v>
       </c>
       <c r="AP8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ8">
         <v>12345</v>
       </c>
       <c r="AR8" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS8" s="3">
         <v>45399</v>
       </c>
       <c r="AT8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU8" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW8" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX8" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY8" t="s">
         <v>73</v>
       </c>
-      <c r="AU8" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW8" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX8" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY8" t="s">
+      <c r="AZ8" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="BI8" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="AZ8" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="BI8" s="1" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B9" t="s">
         <v>102</v>
       </c>
-      <c r="B9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
+      <c r="C9" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D9" t="b">
         <v>0</v>
@@ -3261,28 +3265,28 @@
         <v>45399</v>
       </c>
       <c r="I9" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J9" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="K9">
         <v>17986</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M9" s="21">
         <v>45773</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q9">
         <v>0</v>
@@ -3301,7 +3305,7 @@
         <v>123.23</v>
       </c>
       <c r="AG9" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH9">
         <f t="shared" si="0"/>
@@ -3315,48 +3319,48 @@
         <v>59.91</v>
       </c>
       <c r="AP9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ9">
         <v>12346</v>
       </c>
       <c r="AR9" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS9" s="3">
         <v>45399</v>
       </c>
       <c r="AT9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU9" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW9" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX9" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY9" t="s">
         <v>73</v>
       </c>
-      <c r="AU9" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW9" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX9" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY9" t="s">
+      <c r="AZ9" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="BI9" s="16" t="s">
         <v>74</v>
-      </c>
-      <c r="AZ9" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="BI9" s="16" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B10" t="s">
         <v>102</v>
       </c>
-      <c r="B10" t="s">
-        <v>103</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
+      <c r="C10" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D10" t="b">
         <v>0</v>
@@ -3368,28 +3372,28 @@
         <v>45399</v>
       </c>
       <c r="I10" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J10" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="K10">
         <v>17983</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M10" s="21">
         <v>45773</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -3408,7 +3412,7 @@
         <v>47.18</v>
       </c>
       <c r="AG10" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH10">
         <f t="shared" si="0"/>
@@ -3422,48 +3426,48 @@
         <v>22.93</v>
       </c>
       <c r="AP10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ10">
         <v>12347</v>
       </c>
       <c r="AR10" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS10" s="3">
         <v>45399</v>
       </c>
       <c r="AT10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY10" t="s">
         <v>73</v>
       </c>
-      <c r="AU10" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW10" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX10" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY10" t="s">
+      <c r="AZ10" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="BI10" s="16" t="s">
         <v>74</v>
-      </c>
-      <c r="AZ10" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="BI10" s="16" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="11" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B11" t="s">
         <v>102</v>
       </c>
-      <c r="B11" t="s">
-        <v>103</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
+      <c r="C11" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D11" t="b">
         <v>0</v>
@@ -3475,28 +3479,28 @@
         <v>45399</v>
       </c>
       <c r="I11" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J11" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="K11">
         <v>17982</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M11" s="21">
         <v>45773</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P11" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -3515,7 +3519,7 @@
         <v>25.58</v>
       </c>
       <c r="AG11" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH11">
         <f t="shared" si="0"/>
@@ -3529,48 +3533,48 @@
         <v>12.43</v>
       </c>
       <c r="AP11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ11">
         <v>12348</v>
       </c>
       <c r="AR11" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS11" s="3">
         <v>45399</v>
       </c>
       <c r="AT11" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX11" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY11" t="s">
         <v>73</v>
       </c>
-      <c r="AU11" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW11" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX11" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY11" t="s">
+      <c r="AZ11" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="BI11" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="AZ11" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="BI11" s="1" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="12" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B12" t="s">
-        <v>99</v>
-      </c>
-      <c r="C12">
-        <v>1</v>
+        <v>98</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D12" t="b">
         <v>0</v>
@@ -3582,25 +3586,25 @@
         <v>45399</v>
       </c>
       <c r="I12" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J12" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="K12">
         <v>1681</v>
       </c>
       <c r="L12" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="O12" t="s">
+        <v>68</v>
+      </c>
+      <c r="P12" s="14" t="s">
         <v>107</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="O12" t="s">
-        <v>69</v>
-      </c>
-      <c r="P12" s="14" t="s">
-        <v>108</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -3619,7 +3623,7 @@
         <v>9.06</v>
       </c>
       <c r="AG12" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH12">
         <f t="shared" si="0"/>
@@ -3633,45 +3637,45 @@
         <v>4.4000000000000004</v>
       </c>
       <c r="AP12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ12">
         <v>12349</v>
       </c>
       <c r="AR12" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS12" s="3">
         <v>45399</v>
       </c>
       <c r="AT12" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU12" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW12" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX12" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY12" t="s">
         <v>73</v>
       </c>
-      <c r="AU12" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW12" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX12" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY12" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ12" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B13" t="s">
         <v>109</v>
       </c>
-      <c r="B13" t="s">
-        <v>110</v>
-      </c>
-      <c r="C13">
-        <v>1</v>
+      <c r="C13" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D13" t="b">
         <v>0</v>
@@ -3683,28 +3687,28 @@
         <v>45400</v>
       </c>
       <c r="I13" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J13" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="K13">
         <v>505</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M13" s="21">
         <v>45659</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q13">
         <v>0</v>
@@ -3723,7 +3727,7 @@
         <v>1.26</v>
       </c>
       <c r="AG13" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AH13">
         <f t="shared" si="0"/>
@@ -3736,45 +3740,45 @@
         <v>0.3</v>
       </c>
       <c r="AP13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ13">
         <v>12341</v>
       </c>
       <c r="AR13" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS13" s="3">
         <v>45400</v>
       </c>
       <c r="AT13" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU13" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW13" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX13" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY13" t="s">
         <v>73</v>
       </c>
-      <c r="AU13" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW13" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX13" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY13" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ13" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B14" t="s">
         <v>109</v>
       </c>
-      <c r="B14" t="s">
-        <v>110</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
+      <c r="C14" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D14" t="b">
         <v>0</v>
@@ -3786,28 +3790,28 @@
         <v>45400</v>
       </c>
       <c r="I14" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J14" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="K14">
         <v>504</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M14" s="21">
         <v>45659</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -3826,7 +3830,7 @@
         <v>11.76</v>
       </c>
       <c r="AG14" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AH14">
         <f t="shared" si="0"/>
@@ -3839,45 +3843,45 @@
         <v>2.8</v>
       </c>
       <c r="AP14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ14">
         <v>12342</v>
       </c>
       <c r="AR14" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS14" s="3">
         <v>45400</v>
       </c>
       <c r="AT14" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU14" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW14" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX14" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY14" t="s">
         <v>73</v>
       </c>
-      <c r="AU14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX14" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY14" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ14" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B15" t="s">
         <v>102</v>
       </c>
-      <c r="B15" t="s">
-        <v>103</v>
-      </c>
-      <c r="C15">
-        <v>1</v>
+      <c r="C15" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D15" t="b">
         <v>0</v>
@@ -3889,28 +3893,28 @@
         <v>45400</v>
       </c>
       <c r="I15" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J15" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="K15">
         <v>18028</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M15" s="21">
         <v>45773</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O15" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -3929,7 +3933,7 @@
         <v>23.93</v>
       </c>
       <c r="AG15" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH15">
         <f t="shared" si="0"/>
@@ -3943,48 +3947,48 @@
         <v>11.63</v>
       </c>
       <c r="AP15" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ15">
         <v>12368</v>
       </c>
       <c r="AR15" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS15" s="3">
         <v>45400</v>
       </c>
       <c r="AT15" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU15" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW15" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX15" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY15" t="s">
         <v>73</v>
       </c>
-      <c r="AU15" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW15" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX15" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY15" t="s">
+      <c r="AZ15" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="BI15" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="AZ15" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="BI15" s="1" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B16" t="s">
         <v>102</v>
       </c>
-      <c r="B16" t="s">
-        <v>103</v>
-      </c>
-      <c r="C16">
-        <v>1</v>
+      <c r="C16" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D16" t="b">
         <v>0</v>
@@ -3996,28 +4000,28 @@
         <v>45400</v>
       </c>
       <c r="I16" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J16" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="K16">
         <v>18029</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M16" s="21">
         <v>45773</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q16">
         <v>0</v>
@@ -4036,7 +4040,7 @@
         <v>0.89</v>
       </c>
       <c r="AG16" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH16">
         <f t="shared" si="0"/>
@@ -4050,45 +4054,45 @@
         <v>0.43</v>
       </c>
       <c r="AP16" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ16">
         <v>12369</v>
       </c>
       <c r="AR16" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS16" s="3">
         <v>45400</v>
       </c>
       <c r="AT16" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU16" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW16" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX16" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY16" t="s">
         <v>73</v>
       </c>
-      <c r="AU16" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW16" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX16" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY16" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ16" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B17" t="s">
         <v>109</v>
       </c>
-      <c r="B17" t="s">
-        <v>110</v>
-      </c>
-      <c r="C17">
-        <v>1</v>
+      <c r="C17" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D17" t="b">
         <v>0</v>
@@ -4100,28 +4104,28 @@
         <v>45401</v>
       </c>
       <c r="I17" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J17" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="K17">
         <v>512</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M17" s="21">
         <v>45659</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q17">
         <v>0</v>
@@ -4140,7 +4144,7 @@
         <v>3.46</v>
       </c>
       <c r="AG17" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH17">
         <f t="shared" si="0"/>
@@ -4154,45 +4158,45 @@
         <v>1.68</v>
       </c>
       <c r="AP17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ17">
         <v>12337</v>
       </c>
       <c r="AR17" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS17" s="3">
         <v>45401</v>
       </c>
       <c r="AT17" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU17" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW17" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX17" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY17" t="s">
         <v>73</v>
       </c>
-      <c r="AU17" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW17" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX17" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY17" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ17" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B18" t="s">
         <v>109</v>
       </c>
-      <c r="B18" t="s">
-        <v>110</v>
-      </c>
-      <c r="C18">
-        <v>1</v>
+      <c r="C18" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D18" t="b">
         <v>0</v>
@@ -4204,28 +4208,28 @@
         <v>45401</v>
       </c>
       <c r="I18" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J18" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="K18">
         <v>514</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M18" s="21">
         <v>45659</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O18" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P18" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q18">
         <v>0</v>
@@ -4244,7 +4248,7 @@
         <v>6.14</v>
       </c>
       <c r="AG18" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH18">
         <f t="shared" si="0"/>
@@ -4258,45 +4262,45 @@
         <v>2.99</v>
       </c>
       <c r="AP18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ18">
         <v>12338</v>
       </c>
       <c r="AR18" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS18" s="3">
         <v>45401</v>
       </c>
       <c r="AT18" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU18" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW18" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX18" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY18" t="s">
         <v>73</v>
       </c>
-      <c r="AU18" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW18" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX18" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY18" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ18" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B19" t="s">
         <v>109</v>
       </c>
-      <c r="B19" t="s">
-        <v>110</v>
-      </c>
-      <c r="C19">
-        <v>1</v>
+      <c r="C19" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D19" t="b">
         <v>0</v>
@@ -4308,28 +4312,28 @@
         <v>45401</v>
       </c>
       <c r="I19" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J19" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="K19">
         <v>511</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M19" s="21">
         <v>45659</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P19" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q19">
         <v>0</v>
@@ -4348,7 +4352,7 @@
         <v>13.44</v>
       </c>
       <c r="AG19" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AH19">
         <f t="shared" si="0"/>
@@ -4361,45 +4365,45 @@
         <v>3.2</v>
       </c>
       <c r="AP19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ19">
         <v>12339</v>
       </c>
       <c r="AR19" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS19" s="3">
         <v>45401</v>
       </c>
       <c r="AT19" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU19" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW19" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX19" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY19" t="s">
         <v>73</v>
       </c>
-      <c r="AU19" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW19" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX19" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY19" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ19" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B20" t="s">
         <v>109</v>
       </c>
-      <c r="B20" t="s">
-        <v>110</v>
-      </c>
-      <c r="C20">
-        <v>1</v>
+      <c r="C20" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D20" t="b">
         <v>0</v>
@@ -4411,28 +4415,28 @@
         <v>45401</v>
       </c>
       <c r="I20" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J20" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="K20">
         <v>509</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M20" s="21">
         <v>45659</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -4451,7 +4455,7 @@
         <v>8.4</v>
       </c>
       <c r="AG20" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AH20">
         <f t="shared" si="0"/>
@@ -4464,45 +4468,45 @@
         <v>2</v>
       </c>
       <c r="AP20" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ20">
         <v>12340</v>
       </c>
       <c r="AR20" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS20" s="3">
         <v>45401</v>
       </c>
       <c r="AT20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU20" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW20" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX20" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY20" t="s">
         <v>73</v>
       </c>
-      <c r="AU20" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW20" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX20" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY20" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ20" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B21" t="s">
         <v>109</v>
       </c>
-      <c r="B21" t="s">
-        <v>110</v>
-      </c>
-      <c r="C21">
-        <v>1</v>
+      <c r="C21" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D21" t="b">
         <v>0</v>
@@ -4514,28 +4518,28 @@
         <v>45401</v>
       </c>
       <c r="I21" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J21" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="K21">
         <v>510</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M21" s="21">
         <v>45659</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P21" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q21">
         <v>0</v>
@@ -4554,7 +4558,7 @@
         <v>25.2</v>
       </c>
       <c r="AG21" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AH21">
         <f t="shared" si="0"/>
@@ -4567,45 +4571,45 @@
         <v>6</v>
       </c>
       <c r="AP21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ21">
         <v>12343</v>
       </c>
       <c r="AR21" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS21" s="3">
         <v>45401</v>
       </c>
       <c r="AT21" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU21" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW21" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX21" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY21" t="s">
         <v>73</v>
       </c>
-      <c r="AU21" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW21" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX21" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY21" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ21" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B22" t="s">
         <v>109</v>
       </c>
-      <c r="B22" t="s">
-        <v>110</v>
-      </c>
-      <c r="C22">
-        <v>1</v>
+      <c r="C22" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D22" t="b">
         <v>0</v>
@@ -4617,28 +4621,28 @@
         <v>45401</v>
       </c>
       <c r="I22" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J22" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="K22">
         <v>516</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M22" s="21">
         <v>45659</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O22" t="s">
+        <v>68</v>
+      </c>
+      <c r="P22" t="s">
         <v>69</v>
-      </c>
-      <c r="P22" t="s">
-        <v>70</v>
       </c>
       <c r="Q22">
         <v>0</v>
@@ -4657,7 +4661,7 @@
         <v>25.2</v>
       </c>
       <c r="AG22" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AH22">
         <f t="shared" si="0"/>
@@ -4670,45 +4674,45 @@
         <v>6</v>
       </c>
       <c r="AP22" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ22">
         <v>12344</v>
       </c>
       <c r="AR22" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS22" s="3">
         <v>45401</v>
       </c>
       <c r="AT22" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU22" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW22" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX22" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY22" t="s">
         <v>73</v>
       </c>
-      <c r="AU22" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW22" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX22" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY22" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ22" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B23" t="s">
         <v>102</v>
       </c>
-      <c r="B23" t="s">
-        <v>103</v>
-      </c>
-      <c r="C23">
-        <v>1</v>
+      <c r="C23" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D23" t="b">
         <v>0</v>
@@ -4720,28 +4724,28 @@
         <v>45403</v>
       </c>
       <c r="I23" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J23" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="K23">
         <v>18159</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M23" s="21">
         <v>45773</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O23" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P23" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q23">
         <v>0</v>
@@ -4760,7 +4764,7 @@
         <v>6.41</v>
       </c>
       <c r="AG23" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH23">
         <f t="shared" si="0"/>
@@ -4774,45 +4778,45 @@
         <v>3.12</v>
       </c>
       <c r="AP23" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ23">
         <v>12350</v>
       </c>
       <c r="AR23" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS23" s="3">
         <v>45403</v>
       </c>
       <c r="AT23" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU23" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW23" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX23" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY23" t="s">
         <v>73</v>
       </c>
-      <c r="AU23" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW23" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX23" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY23" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ23" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B24" t="s">
         <v>112</v>
       </c>
-      <c r="B24" t="s">
-        <v>113</v>
-      </c>
-      <c r="C24">
-        <v>1</v>
+      <c r="C24" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D24" t="b">
         <v>0</v>
@@ -4824,28 +4828,28 @@
         <v>45403</v>
       </c>
       <c r="I24" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J24" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="K24">
         <v>164</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M24" s="21">
         <v>45437</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O24" t="s">
+        <v>78</v>
+      </c>
+      <c r="P24" t="s">
         <v>79</v>
-      </c>
-      <c r="P24" t="s">
-        <v>80</v>
       </c>
       <c r="Q24">
         <v>40</v>
@@ -4861,7 +4865,7 @@
         <v>0</v>
       </c>
       <c r="AG24" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH24">
         <f t="shared" si="0"/>
@@ -4875,45 +4879,45 @@
         <v>0.7</v>
       </c>
       <c r="AP24" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ24">
         <v>12351</v>
       </c>
       <c r="AR24" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS24" s="3">
         <v>45403</v>
       </c>
       <c r="AT24" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU24" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW24" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX24" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY24" t="s">
         <v>73</v>
       </c>
-      <c r="AU24" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW24" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX24" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY24" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ24" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B25" t="s">
         <v>112</v>
       </c>
-      <c r="B25" t="s">
-        <v>113</v>
-      </c>
-      <c r="C25">
-        <v>1</v>
+      <c r="C25" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D25" t="b">
         <v>0</v>
@@ -4925,28 +4929,28 @@
         <v>45403</v>
       </c>
       <c r="I25" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J25" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="K25">
         <v>165</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M25" s="21">
         <v>45437</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O25" t="s">
+        <v>78</v>
+      </c>
+      <c r="P25" t="s">
         <v>79</v>
-      </c>
-      <c r="P25" t="s">
-        <v>80</v>
       </c>
       <c r="Q25">
         <v>15</v>
@@ -4962,7 +4966,7 @@
         <v>0</v>
       </c>
       <c r="AG25" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH25">
         <f t="shared" si="0"/>
@@ -4976,45 +4980,45 @@
         <v>0.26</v>
       </c>
       <c r="AP25" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ25">
         <v>12352</v>
       </c>
       <c r="AR25" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS25" s="3">
         <v>45403</v>
       </c>
       <c r="AT25" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU25" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW25" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX25" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY25" t="s">
         <v>73</v>
       </c>
-      <c r="AU25" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW25" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX25" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY25" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ25" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B26" t="s">
         <v>115</v>
       </c>
-      <c r="B26" t="s">
-        <v>116</v>
-      </c>
-      <c r="C26">
-        <v>1</v>
+      <c r="C26" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D26" t="b">
         <v>0</v>
@@ -5026,28 +5030,28 @@
         <v>45406</v>
       </c>
       <c r="I26" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J26" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="K26">
         <v>887</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M26" s="21">
         <v>45647</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P26" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q26">
         <v>0</v>
@@ -5066,7 +5070,7 @@
         <v>21</v>
       </c>
       <c r="AG26" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AH26">
         <f t="shared" si="0"/>
@@ -5079,45 +5083,45 @@
         <v>5</v>
       </c>
       <c r="AP26" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ26">
         <v>12353</v>
       </c>
       <c r="AR26" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS26" s="3">
         <v>45406</v>
       </c>
       <c r="AT26" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU26" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW26" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX26" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY26" t="s">
         <v>73</v>
       </c>
-      <c r="AU26" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW26" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX26" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY26" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ26" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B27" t="s">
         <v>118</v>
       </c>
-      <c r="B27" t="s">
-        <v>119</v>
-      </c>
-      <c r="C27">
-        <v>1</v>
+      <c r="C27" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D27" t="b">
         <v>0</v>
@@ -5129,28 +5133,28 @@
         <v>45406</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K27">
         <v>2765</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M27" s="21">
         <v>45647</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O27" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P27" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q27">
         <v>0</v>
@@ -5169,7 +5173,7 @@
         <v>10.71</v>
       </c>
       <c r="AG27" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH27">
         <f t="shared" si="0"/>
@@ -5183,45 +5187,45 @@
         <v>5.21</v>
       </c>
       <c r="AP27" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ27">
         <v>12354</v>
       </c>
       <c r="AR27" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS27" s="3">
         <v>45406</v>
       </c>
       <c r="AT27" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU27" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW27" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX27" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY27" t="s">
         <v>73</v>
       </c>
-      <c r="AU27" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW27" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX27" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY27" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ27" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B28" t="s">
         <v>122</v>
       </c>
-      <c r="B28" t="s">
-        <v>123</v>
-      </c>
-      <c r="C28">
-        <v>1</v>
+      <c r="C28" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D28" t="b">
         <v>0</v>
@@ -5233,28 +5237,28 @@
         <v>45406</v>
       </c>
       <c r="I28" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J28" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="K28">
         <v>229</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M28" s="21">
         <v>45753</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O28" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P28" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q28">
         <v>0</v>
@@ -5273,7 +5277,7 @@
         <v>24.84</v>
       </c>
       <c r="AG28" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH28">
         <f t="shared" si="0"/>
@@ -5287,48 +5291,48 @@
         <v>12.08</v>
       </c>
       <c r="AP28" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ28">
         <v>12355</v>
       </c>
       <c r="AR28" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS28" s="3">
         <v>45406</v>
       </c>
       <c r="AT28" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU28" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW28" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX28" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY28" t="s">
         <v>73</v>
       </c>
-      <c r="AU28" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW28" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX28" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY28" t="s">
+      <c r="AZ28" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="BI28" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="AZ28" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="BI28" s="1" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="29" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B29" t="s">
         <v>122</v>
       </c>
-      <c r="B29" t="s">
-        <v>123</v>
-      </c>
-      <c r="C29">
-        <v>1</v>
+      <c r="C29" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D29" t="b">
         <v>0</v>
@@ -5340,28 +5344,28 @@
         <v>45406</v>
       </c>
       <c r="I29" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J29" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="K29">
         <v>232</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M29" s="21">
         <v>45437</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O29" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P29" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q29">
         <v>0</v>
@@ -5380,7 +5384,7 @@
         <v>0.25</v>
       </c>
       <c r="AG29" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH29">
         <f t="shared" si="0"/>
@@ -5394,45 +5398,45 @@
         <v>0.12</v>
       </c>
       <c r="AP29" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ29">
         <v>12356</v>
       </c>
       <c r="AR29" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS29" s="3">
         <v>45406</v>
       </c>
       <c r="AT29" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU29" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW29" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX29" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY29" t="s">
         <v>73</v>
       </c>
-      <c r="AU29" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW29" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX29" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY29" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ29" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B30" t="s">
         <v>122</v>
       </c>
-      <c r="B30" t="s">
-        <v>123</v>
-      </c>
-      <c r="C30">
-        <v>1</v>
+      <c r="C30" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D30" t="b">
         <v>0</v>
@@ -5444,28 +5448,28 @@
         <v>45406</v>
       </c>
       <c r="I30" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J30" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="K30">
         <v>230</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M30" s="21">
         <v>45437</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O30" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q30">
         <v>0</v>
@@ -5484,7 +5488,7 @@
         <v>10.5</v>
       </c>
       <c r="AG30" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH30">
         <f t="shared" si="0"/>
@@ -5498,45 +5502,45 @@
         <v>5.0999999999999996</v>
       </c>
       <c r="AP30" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ30">
         <v>12357</v>
       </c>
       <c r="AR30" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS30" s="3">
         <v>45406</v>
       </c>
       <c r="AT30" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU30" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW30" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX30" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY30" t="s">
         <v>73</v>
       </c>
-      <c r="AU30" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW30" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX30" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY30" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ30" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="31" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B31" t="s">
         <v>125</v>
       </c>
-      <c r="B31" t="s">
-        <v>126</v>
-      </c>
-      <c r="C31">
-        <v>1</v>
+      <c r="C31" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D31" t="b">
         <v>0</v>
@@ -5548,28 +5552,28 @@
         <v>45406</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K31">
         <v>1540</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="M31" s="21">
         <v>45607</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O31" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P31" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q31">
         <v>0</v>
@@ -5585,7 +5589,7 @@
         <v>738.26</v>
       </c>
       <c r="AG31" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AH31">
         <f t="shared" si="0"/>
@@ -5598,42 +5602,42 @@
         <v>0</v>
       </c>
       <c r="AP31" t="s">
+        <v>72</v>
+      </c>
+      <c r="AR31" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AT31" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU31" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW31" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX31" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY31" t="s">
         <v>73</v>
       </c>
-      <c r="AR31" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT31" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU31" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW31" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX31" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY31" t="s">
+      <c r="AZ31" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="BI31" s="16" t="s">
         <v>74</v>
-      </c>
-      <c r="AZ31" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="BI31" s="16" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="32" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B32" t="s">
         <v>112</v>
       </c>
-      <c r="B32" t="s">
-        <v>113</v>
-      </c>
-      <c r="C32">
-        <v>1</v>
+      <c r="C32" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D32" t="b">
         <v>0</v>
@@ -5645,28 +5649,28 @@
         <v>45406</v>
       </c>
       <c r="I32" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J32" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="K32">
         <v>166</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M32" s="21">
         <v>45437</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O32" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P32" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="Q32">
         <v>50</v>
@@ -5682,7 +5686,7 @@
         <v>0</v>
       </c>
       <c r="AG32" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH32">
         <f t="shared" si="0"/>
@@ -5696,45 +5700,45 @@
         <v>0.88</v>
       </c>
       <c r="AP32" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ32">
         <v>12358</v>
       </c>
       <c r="AR32" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS32" s="3">
         <v>45406</v>
       </c>
       <c r="AT32" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU32" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW32" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX32" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY32" t="s">
         <v>73</v>
       </c>
-      <c r="AU32" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW32" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX32" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY32" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ32" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B33" t="s">
         <v>130</v>
       </c>
-      <c r="B33" t="s">
-        <v>131</v>
-      </c>
-      <c r="C33">
-        <v>1</v>
+      <c r="C33" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D33" t="b">
         <v>0</v>
@@ -5746,28 +5750,28 @@
         <v>45406</v>
       </c>
       <c r="I33" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J33" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="K33">
         <v>260</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="M33" s="21">
         <v>45437</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O33" t="s">
+        <v>78</v>
+      </c>
+      <c r="P33" t="s">
         <v>79</v>
-      </c>
-      <c r="P33" t="s">
-        <v>80</v>
       </c>
       <c r="Q33">
         <v>25</v>
@@ -5783,7 +5787,7 @@
         <v>0</v>
       </c>
       <c r="AG33" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH33">
         <f t="shared" si="0"/>
@@ -5797,45 +5801,45 @@
         <v>0.44</v>
       </c>
       <c r="AP33" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ33">
         <v>12359</v>
       </c>
       <c r="AR33" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS33" s="3">
         <v>45406</v>
       </c>
       <c r="AT33" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU33" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW33" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX33" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY33" t="s">
         <v>73</v>
       </c>
-      <c r="AU33" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW33" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX33" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY33" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ33" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="34" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B34" t="s">
         <v>130</v>
       </c>
-      <c r="B34" t="s">
-        <v>131</v>
-      </c>
-      <c r="C34">
-        <v>1</v>
+      <c r="C34" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D34" t="b">
         <v>0</v>
@@ -5847,28 +5851,28 @@
         <v>45406</v>
       </c>
       <c r="I34" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J34" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="K34">
         <v>261</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="M34" s="21">
         <v>45437</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O34" t="s">
+        <v>78</v>
+      </c>
+      <c r="P34" t="s">
         <v>79</v>
-      </c>
-      <c r="P34" t="s">
-        <v>80</v>
       </c>
       <c r="Q34">
         <v>185</v>
@@ -5884,7 +5888,7 @@
         <v>0</v>
       </c>
       <c r="AG34" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH34">
         <f t="shared" si="0"/>
@@ -5898,45 +5902,45 @@
         <v>3.24</v>
       </c>
       <c r="AP34" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ34">
         <v>12360</v>
       </c>
       <c r="AR34" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS34" s="3">
         <v>45406</v>
       </c>
       <c r="AT34" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU34" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW34" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX34" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY34" t="s">
         <v>73</v>
       </c>
-      <c r="AU34" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW34" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX34" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY34" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ34" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="35" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B35" t="s">
         <v>130</v>
       </c>
-      <c r="B35" t="s">
-        <v>131</v>
-      </c>
-      <c r="C35">
-        <v>1</v>
+      <c r="C35" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D35" t="b">
         <v>0</v>
@@ -5948,28 +5952,28 @@
         <v>45406</v>
       </c>
       <c r="I35" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J35" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="K35">
         <v>263</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="M35" s="21">
         <v>45437</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O35" t="s">
+        <v>78</v>
+      </c>
+      <c r="P35" t="s">
         <v>79</v>
-      </c>
-      <c r="P35" t="s">
-        <v>80</v>
       </c>
       <c r="Q35">
         <v>60</v>
@@ -5985,7 +5989,7 @@
         <v>0</v>
       </c>
       <c r="AG35" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH35">
         <f t="shared" si="0"/>
@@ -5999,45 +6003,45 @@
         <v>1.05</v>
       </c>
       <c r="AP35" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ35">
         <v>12361</v>
       </c>
       <c r="AR35" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS35" s="3">
         <v>45406</v>
       </c>
       <c r="AT35" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU35" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW35" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX35" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY35" t="s">
         <v>73</v>
       </c>
-      <c r="AU35" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW35" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX35" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY35" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ35" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="36" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B36" t="s">
         <v>122</v>
       </c>
-      <c r="B36" t="s">
-        <v>123</v>
-      </c>
-      <c r="C36">
-        <v>1</v>
+      <c r="C36" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D36" t="b">
         <v>0</v>
@@ -6049,28 +6053,28 @@
         <v>45406</v>
       </c>
       <c r="I36" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J36" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="J36" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="K36">
         <v>233</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M36" s="21">
         <v>45437</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O36" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P36" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q36">
         <v>0</v>
@@ -6089,7 +6093,7 @@
         <v>6.72</v>
       </c>
       <c r="AG36" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AH36">
         <f t="shared" si="0"/>
@@ -6102,45 +6106,45 @@
         <v>1.6</v>
       </c>
       <c r="AP36" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ36">
         <v>12362</v>
       </c>
       <c r="AR36" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS36" s="3">
         <v>45406</v>
       </c>
       <c r="AT36" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU36" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW36" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX36" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY36" t="s">
         <v>73</v>
       </c>
-      <c r="AU36" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW36" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX36" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY36" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ36" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="37" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B37" t="s">
         <v>115</v>
       </c>
-      <c r="B37" t="s">
-        <v>116</v>
-      </c>
-      <c r="C37">
-        <v>1</v>
+      <c r="C37" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D37" t="b">
         <v>0</v>
@@ -6152,28 +6156,28 @@
         <v>45406</v>
       </c>
       <c r="I37" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J37" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="K37">
         <v>889</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M37" s="21">
         <v>45647</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O37" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P37" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q37">
         <v>0</v>
@@ -6192,7 +6196,7 @@
         <v>183.12</v>
       </c>
       <c r="AG37" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AH37">
         <f t="shared" si="0"/>
@@ -6205,48 +6209,48 @@
         <v>43.6</v>
       </c>
       <c r="AP37" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ37">
         <v>12363</v>
       </c>
       <c r="AR37" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS37" s="3">
         <v>45406</v>
       </c>
       <c r="AT37" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU37" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW37" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX37" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY37" t="s">
         <v>73</v>
       </c>
-      <c r="AU37" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW37" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX37" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY37" t="s">
+      <c r="AZ37" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="BI37" s="16" t="s">
         <v>74</v>
-      </c>
-      <c r="AZ37" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="BI37" s="16" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="38" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B38" t="s">
         <v>133</v>
       </c>
-      <c r="B38" t="s">
-        <v>134</v>
-      </c>
-      <c r="C38">
-        <v>1</v>
+      <c r="C38" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D38" t="b">
         <v>0</v>
@@ -6258,28 +6262,28 @@
         <v>45407</v>
       </c>
       <c r="I38" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J38" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="J38" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="K38">
         <v>5</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M38" s="21">
         <v>45607</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O38" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P38" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q38">
         <v>0</v>
@@ -6298,7 +6302,7 @@
         <v>2033.09</v>
       </c>
       <c r="AG38" s="15" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH38">
         <f t="shared" si="0"/>
@@ -6312,48 +6316,48 @@
         <v>988.31</v>
       </c>
       <c r="AP38" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ38">
         <v>12330</v>
       </c>
       <c r="AR38" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS38" s="3">
         <v>45407</v>
       </c>
       <c r="AT38" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU38" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW38" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX38" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY38" t="s">
         <v>73</v>
       </c>
-      <c r="AU38" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW38" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX38" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY38" t="s">
+      <c r="AZ38" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="BI38" s="16" t="s">
         <v>74</v>
-      </c>
-      <c r="AZ38" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="BI38" s="16" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="39" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B39" t="s">
         <v>137</v>
       </c>
-      <c r="B39" t="s">
-        <v>138</v>
-      </c>
-      <c r="C39">
-        <v>1</v>
+      <c r="C39" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D39" t="b">
         <v>0</v>
@@ -6365,28 +6369,28 @@
         <v>45407</v>
       </c>
       <c r="I39" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J39" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="J39" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="K39">
         <v>256</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="M39" s="21">
         <v>45437</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O39" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P39" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q39">
         <v>0</v>
@@ -6405,7 +6409,7 @@
         <v>319.2</v>
       </c>
       <c r="AG39" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AH39">
         <f t="shared" si="0"/>
@@ -6418,48 +6422,48 @@
         <v>266</v>
       </c>
       <c r="AP39" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ39">
         <v>12332</v>
       </c>
       <c r="AR39" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS39" s="3">
         <v>45407</v>
       </c>
       <c r="AT39" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU39" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW39" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX39" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY39" t="s">
         <v>73</v>
       </c>
-      <c r="AU39" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW39" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX39" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY39" t="s">
+      <c r="AZ39" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="BI39" s="16" t="s">
         <v>74</v>
-      </c>
-      <c r="AZ39" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="BI39" s="16" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="40" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B40" t="s">
         <v>141</v>
       </c>
-      <c r="B40" t="s">
-        <v>142</v>
-      </c>
-      <c r="C40">
-        <v>1</v>
+      <c r="C40" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D40" t="b">
         <v>0</v>
@@ -6471,28 +6475,28 @@
         <v>45407</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K40">
         <v>807</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="M40" s="21">
         <v>45437</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O40" t="s">
+        <v>78</v>
+      </c>
+      <c r="P40" t="s">
         <v>79</v>
-      </c>
-      <c r="P40" t="s">
-        <v>80</v>
       </c>
       <c r="Q40">
         <v>600</v>
@@ -6508,7 +6512,7 @@
         <v>0</v>
       </c>
       <c r="AG40" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH40">
         <f t="shared" si="0"/>
@@ -6522,48 +6526,48 @@
         <v>10.5</v>
       </c>
       <c r="AP40" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ40">
         <v>12364</v>
       </c>
       <c r="AR40" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS40" s="3">
         <v>45407</v>
       </c>
       <c r="AT40" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU40" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW40" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX40" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY40" t="s">
         <v>73</v>
       </c>
-      <c r="AU40" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW40" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX40" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY40" t="s">
+      <c r="AZ40" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="BI40" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="AZ40" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="BI40" s="1" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="41" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B41" t="s">
         <v>145</v>
       </c>
-      <c r="B41" t="s">
-        <v>146</v>
-      </c>
-      <c r="C41">
-        <v>1</v>
+      <c r="C41" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D41" t="b">
         <v>0</v>
@@ -6575,28 +6579,28 @@
         <v>45407</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K41">
         <v>928</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="M41" s="21">
         <v>45774</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O41" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P41" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q41">
         <v>0</v>
@@ -6615,7 +6619,7 @@
         <v>3.53</v>
       </c>
       <c r="AG41" s="15" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AH41">
         <f t="shared" si="0"/>
@@ -6629,45 +6633,45 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="AP41" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ41">
         <v>12365</v>
       </c>
       <c r="AR41" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS41" s="3">
         <v>45407</v>
       </c>
       <c r="AT41" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU41" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW41" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX41" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY41" t="s">
         <v>73</v>
       </c>
-      <c r="AU41" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW41" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX41" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY41" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ41" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="42" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B42" t="s">
         <v>149</v>
       </c>
-      <c r="B42" t="s">
-        <v>150</v>
-      </c>
-      <c r="C42">
-        <v>1</v>
+      <c r="C42" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D42" t="b">
         <v>0</v>
@@ -6679,28 +6683,28 @@
         <v>45408</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K42">
         <v>5395</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="M42" s="21">
         <v>45672</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O42" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P42" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q42">
         <v>0</v>
@@ -6719,7 +6723,7 @@
         <v>17.04</v>
       </c>
       <c r="AG42" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH42">
         <f t="shared" si="0"/>
@@ -6733,48 +6737,48 @@
         <v>8.2799999999999994</v>
       </c>
       <c r="AP42" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ42">
         <v>12334</v>
       </c>
       <c r="AR42" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS42" s="3">
         <v>45408</v>
       </c>
       <c r="AT42" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU42" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW42" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX42" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY42" t="s">
         <v>73</v>
       </c>
-      <c r="AU42" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW42" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX42" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY42" t="s">
+      <c r="AZ42" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="BI42" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="AZ42" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="BI42" s="1" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="43" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B43" t="s">
         <v>152</v>
       </c>
-      <c r="B43" t="s">
-        <v>153</v>
-      </c>
-      <c r="C43">
-        <v>1</v>
+      <c r="C43" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D43" t="b">
         <v>0</v>
@@ -6786,28 +6790,28 @@
         <v>45408</v>
       </c>
       <c r="I43" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J43" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="J43" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="K43">
         <v>3468</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="M43" s="21">
         <v>45586</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O43" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P43" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q43">
         <v>0</v>
@@ -6826,7 +6830,7 @@
         <v>3.02</v>
       </c>
       <c r="AG43" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH43">
         <f t="shared" si="0"/>
@@ -6840,45 +6844,45 @@
         <v>1.47</v>
       </c>
       <c r="AP43" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ43">
         <v>12366</v>
       </c>
       <c r="AR43" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS43" s="3">
         <v>45408</v>
       </c>
       <c r="AT43" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU43" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW43" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX43" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY43" t="s">
         <v>73</v>
       </c>
-      <c r="AU43" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW43" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX43" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY43" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ43" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="44" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B44" t="s">
         <v>155</v>
       </c>
-      <c r="B44" t="s">
-        <v>156</v>
-      </c>
-      <c r="C44">
-        <v>1</v>
+      <c r="C44" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D44" t="b">
         <v>0</v>
@@ -6890,28 +6894,28 @@
         <v>45408</v>
       </c>
       <c r="I44" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J44" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="J44" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="K44">
         <v>1290</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="M44" s="21">
         <v>45586</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O44" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P44" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q44">
         <v>149.15</v>
@@ -6927,7 +6931,7 @@
         <v>0</v>
       </c>
       <c r="AG44" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH44">
         <f t="shared" si="0"/>
@@ -6941,45 +6945,45 @@
         <v>2.61</v>
       </c>
       <c r="AP44" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ44">
         <v>12367</v>
       </c>
       <c r="AR44" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS44" s="3">
         <v>45408</v>
       </c>
       <c r="AT44" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU44" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW44" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX44" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY44" t="s">
         <v>73</v>
       </c>
-      <c r="AU44" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW44" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX44" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY44" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ44" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="45" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B45" t="s">
         <v>158</v>
       </c>
-      <c r="B45" t="s">
-        <v>159</v>
-      </c>
-      <c r="C45">
-        <v>1</v>
+      <c r="C45" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D45" t="b">
         <v>0</v>
@@ -6991,28 +6995,28 @@
         <v>45409</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K45">
         <v>5292</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="M45" s="21">
         <v>45561</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O45" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P45" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q45">
         <v>0</v>
@@ -7031,7 +7035,7 @@
         <v>180</v>
       </c>
       <c r="AG45" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AH45">
         <f t="shared" si="0"/>
@@ -7044,48 +7048,48 @@
         <v>150</v>
       </c>
       <c r="AP45" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ45">
         <v>12335</v>
       </c>
       <c r="AR45" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS45" s="3">
         <v>45409</v>
       </c>
       <c r="AT45" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU45" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW45" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX45" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY45" t="s">
         <v>73</v>
       </c>
-      <c r="AU45" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW45" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX45" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY45" t="s">
+      <c r="AZ45" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="BI45" s="16" t="s">
         <v>74</v>
-      </c>
-      <c r="AZ45" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="BI45" s="16" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="46" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B46" t="s">
         <v>162</v>
       </c>
-      <c r="B46" t="s">
-        <v>163</v>
-      </c>
-      <c r="C46">
-        <v>1</v>
+      <c r="C46" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D46" t="b">
         <v>0</v>
@@ -7097,28 +7101,28 @@
         <v>45409</v>
       </c>
       <c r="I46" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J46" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="J46" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="K46">
         <v>62</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="M46" s="21">
         <v>45777</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O46" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P46" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q46">
         <v>0</v>
@@ -7137,7 +7141,7 @@
         <v>32.4</v>
       </c>
       <c r="AG46" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH46">
         <f t="shared" si="0"/>
@@ -7151,48 +7155,48 @@
         <v>15.75</v>
       </c>
       <c r="AP46" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ46">
         <v>12370</v>
       </c>
       <c r="AR46" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS46" s="3">
         <v>45409</v>
       </c>
       <c r="AT46" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU46" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW46" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX46" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY46" t="s">
         <v>73</v>
       </c>
-      <c r="AU46" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW46" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX46" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY46" t="s">
+      <c r="AZ46" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="BI46" s="16" t="s">
         <v>74</v>
-      </c>
-      <c r="AZ46" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="BI46" s="16" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="47" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B47" t="s">
         <v>165</v>
       </c>
-      <c r="B47" t="s">
-        <v>166</v>
-      </c>
-      <c r="C47">
-        <v>1</v>
+      <c r="C47" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D47" t="b">
         <v>0</v>
@@ -7204,28 +7208,28 @@
         <v>45409</v>
       </c>
       <c r="I47" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J47" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="J47" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="K47">
         <v>128</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M47" s="21">
         <v>45769</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O47" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P47" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q47">
         <v>0</v>
@@ -7244,7 +7248,7 @@
         <v>30.23</v>
       </c>
       <c r="AG47" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH47">
         <f t="shared" si="0"/>
@@ -7258,48 +7262,48 @@
         <v>14.7</v>
       </c>
       <c r="AP47" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ47">
         <v>12371</v>
       </c>
       <c r="AR47" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS47" s="3">
         <v>45409</v>
       </c>
       <c r="AT47" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU47" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW47" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX47" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY47" t="s">
         <v>73</v>
       </c>
-      <c r="AU47" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW47" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX47" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY47" t="s">
+      <c r="AZ47" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="BI47" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="AZ47" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="BI47" s="1" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="48" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B48" t="s">
         <v>165</v>
       </c>
-      <c r="B48" t="s">
-        <v>166</v>
-      </c>
-      <c r="C48">
-        <v>1</v>
+      <c r="C48" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D48" t="b">
         <v>0</v>
@@ -7311,28 +7315,28 @@
         <v>45409</v>
       </c>
       <c r="I48" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J48" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="J48" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="K48">
         <v>129</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="M48" s="21">
         <v>45769</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P48" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q48">
         <v>1846</v>
@@ -7348,7 +7352,7 @@
         <v>0</v>
       </c>
       <c r="AG48" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AH48">
         <f t="shared" si="0"/>
@@ -7362,48 +7366,48 @@
         <v>32.31</v>
       </c>
       <c r="AP48" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ48">
         <v>12372</v>
       </c>
       <c r="AR48" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS48" s="3">
         <v>45409</v>
       </c>
       <c r="AT48" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU48" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW48" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX48" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY48" t="s">
         <v>73</v>
       </c>
-      <c r="AU48" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW48" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX48" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY48" t="s">
+      <c r="AZ48" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="BI48" s="16" t="s">
         <v>74</v>
-      </c>
-      <c r="AZ48" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="BI48" s="16" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="49" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B49" t="s">
         <v>168</v>
       </c>
-      <c r="B49" t="s">
-        <v>169</v>
-      </c>
-      <c r="C49">
-        <v>1</v>
+      <c r="C49" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D49" t="b">
         <v>0</v>
@@ -7415,28 +7419,28 @@
         <v>45410</v>
       </c>
       <c r="I49" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J49" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="J49" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="K49">
         <v>672</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="M49" s="21">
         <v>45697</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O49" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P49" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q49">
         <v>0</v>
@@ -7455,7 +7459,7 @@
         <v>126</v>
       </c>
       <c r="AG49" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="AH49">
         <f t="shared" si="0"/>
@@ -7468,48 +7472,48 @@
         <v>30</v>
       </c>
       <c r="AP49" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ49">
         <v>12373</v>
       </c>
       <c r="AR49" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS49" s="3">
         <v>45410</v>
       </c>
       <c r="AT49" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU49" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW49" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX49" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY49" t="s">
         <v>73</v>
       </c>
-      <c r="AU49" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW49" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX49" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY49" t="s">
+      <c r="AZ49" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="BI49" s="16" t="s">
         <v>74</v>
-      </c>
-      <c r="AZ49" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="BI49" s="16" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="50" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B50" t="s">
         <v>171</v>
       </c>
-      <c r="B50" t="s">
-        <v>172</v>
-      </c>
-      <c r="C50">
-        <v>1</v>
+      <c r="C50" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D50" t="b">
         <v>0</v>
@@ -7521,28 +7525,28 @@
         <v>45410</v>
       </c>
       <c r="I50" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J50" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="J50" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="K50">
         <v>305</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="M50" s="21">
         <v>45644</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O50" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="P50" t="s">
         <v>79</v>
-      </c>
-      <c r="P50" t="s">
-        <v>80</v>
       </c>
       <c r="Q50">
         <v>0</v>
@@ -7561,7 +7565,7 @@
         <v>105.6</v>
       </c>
       <c r="AG50" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AH50">
         <f t="shared" si="0"/>
@@ -7574,48 +7578,48 @@
         <v>88</v>
       </c>
       <c r="AP50" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ50">
         <v>12374</v>
       </c>
       <c r="AR50" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS50" s="3">
         <v>45410</v>
       </c>
       <c r="AT50" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU50" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW50" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX50" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY50" t="s">
         <v>73</v>
       </c>
-      <c r="AU50" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW50" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX50" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY50" t="s">
+      <c r="AZ50" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="BI50" s="16" t="s">
         <v>74</v>
-      </c>
-      <c r="AZ50" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="BI50" s="16" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="51" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B51" t="s">
         <v>168</v>
       </c>
-      <c r="B51" t="s">
-        <v>169</v>
-      </c>
-      <c r="C51">
-        <v>1</v>
+      <c r="C51" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D51" t="b">
         <v>0</v>
@@ -7627,28 +7631,28 @@
         <v>45410</v>
       </c>
       <c r="I51" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J51" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="J51" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="K51">
         <v>673</v>
       </c>
       <c r="L51" s="15" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="M51" s="21">
         <v>45697</v>
       </c>
       <c r="N51" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O51" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="P51" s="5" t="s">
         <v>79</v>
-      </c>
-      <c r="P51" s="5" t="s">
-        <v>80</v>
       </c>
       <c r="Q51">
         <v>0</v>
@@ -7664,7 +7668,7 @@
         <v>0</v>
       </c>
       <c r="AG51" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AH51">
         <v>300</v>
@@ -7685,48 +7689,48 @@
         <v>2015</v>
       </c>
       <c r="AP51" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ51">
         <v>12373</v>
       </c>
       <c r="AR51" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS51" s="3">
         <v>45410</v>
       </c>
       <c r="AT51" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU51" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW51" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX51" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY51" t="s">
         <v>73</v>
       </c>
-      <c r="AU51" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW51" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX51" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY51" t="s">
+      <c r="AZ51" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="BI51" s="16" t="s">
         <v>74</v>
-      </c>
-      <c r="AZ51" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="BI51" s="16" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="52" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B52" t="s">
         <v>176</v>
       </c>
-      <c r="B52" t="s">
-        <v>177</v>
-      </c>
-      <c r="C52">
-        <v>1</v>
+      <c r="C52" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D52" t="b">
         <v>0</v>
@@ -7738,28 +7742,28 @@
         <v>45387</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K52">
         <v>8508485</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M52" s="21">
         <v>45560</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O52" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P52" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="Q52">
         <v>38.29</v>
@@ -7775,7 +7779,7 @@
         <v>0</v>
       </c>
       <c r="AG52" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AH52">
         <f t="shared" si="0"/>
@@ -7788,39 +7792,39 @@
         <v>0</v>
       </c>
       <c r="AP52" t="s">
+        <v>72</v>
+      </c>
+      <c r="AR52" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AT52" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU52" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW52" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX52" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY52" t="s">
         <v>73</v>
       </c>
-      <c r="AR52" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT52" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU52" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW52" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX52" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY52" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ52" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="53" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B53" t="s">
-        <v>181</v>
-      </c>
-      <c r="C53">
-        <v>1</v>
+        <v>180</v>
+      </c>
+      <c r="C53" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D53" t="b">
         <v>0</v>
@@ -7832,28 +7836,28 @@
         <v>45387</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K53">
         <v>1035226</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M53" s="21">
         <v>45560</v>
       </c>
       <c r="N53" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O53" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P53" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q53">
         <v>35.590000000000003</v>
@@ -7869,7 +7873,7 @@
         <v>0</v>
       </c>
       <c r="AG53" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AH53">
         <f t="shared" si="0"/>
@@ -7882,39 +7886,39 @@
         <v>0</v>
       </c>
       <c r="AP53" t="s">
+        <v>72</v>
+      </c>
+      <c r="AR53" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AT53" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU53" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW53" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX53" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY53" t="s">
         <v>73</v>
       </c>
-      <c r="AR53" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT53" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU53" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW53" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX53" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY53" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ53" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="54" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B54" t="s">
-        <v>181</v>
-      </c>
-      <c r="C54">
-        <v>1</v>
+        <v>180</v>
+      </c>
+      <c r="C54" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D54" t="b">
         <v>0</v>
@@ -7926,28 +7930,28 @@
         <v>45387</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K54">
         <v>1035330</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M54" s="21">
         <v>45560</v>
       </c>
       <c r="N54" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O54" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P54" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q54">
         <v>15.35</v>
@@ -7963,7 +7967,7 @@
         <v>0</v>
       </c>
       <c r="AG54" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AH54">
         <f t="shared" si="0"/>
@@ -7976,39 +7980,39 @@
         <v>0</v>
       </c>
       <c r="AP54" t="s">
+        <v>72</v>
+      </c>
+      <c r="AR54" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AT54" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU54" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW54" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX54" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY54" t="s">
         <v>73</v>
       </c>
-      <c r="AR54" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT54" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU54" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW54" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX54" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY54" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ54" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="55" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B55" t="s">
-        <v>181</v>
-      </c>
-      <c r="C55">
-        <v>1</v>
+        <v>180</v>
+      </c>
+      <c r="C55" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D55" t="b">
         <v>0</v>
@@ -8020,28 +8024,28 @@
         <v>45387</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K55">
         <v>1035381</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M55" s="21">
         <v>45560</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O55" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P55" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q55">
         <v>36.18</v>
@@ -8057,7 +8061,7 @@
         <v>0</v>
       </c>
       <c r="AG55" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AH55">
         <f t="shared" si="0"/>
@@ -8070,39 +8074,39 @@
         <v>0</v>
       </c>
       <c r="AP55" t="s">
+        <v>72</v>
+      </c>
+      <c r="AR55" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AT55" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU55" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW55" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX55" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY55" t="s">
         <v>73</v>
       </c>
-      <c r="AR55" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT55" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU55" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW55" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX55" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY55" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ55" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="56" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B56" t="s">
-        <v>181</v>
-      </c>
-      <c r="C56">
-        <v>1</v>
+        <v>180</v>
+      </c>
+      <c r="C56" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D56" t="b">
         <v>0</v>
@@ -8114,28 +8118,28 @@
         <v>45387</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J56" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K56">
         <v>1035852</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M56" s="21">
         <v>45560</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O56" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P56" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q56">
         <v>191.27</v>
@@ -8151,7 +8155,7 @@
         <v>0</v>
       </c>
       <c r="AG56" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AH56">
         <f t="shared" si="0"/>
@@ -8164,39 +8168,39 @@
         <v>0</v>
       </c>
       <c r="AP56" t="s">
+        <v>72</v>
+      </c>
+      <c r="AR56" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AT56" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU56" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW56" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX56" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY56" t="s">
         <v>73</v>
       </c>
-      <c r="AR56" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT56" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU56" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW56" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX56" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY56" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ56" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="57" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B57" t="s">
-        <v>181</v>
-      </c>
-      <c r="C57">
-        <v>1</v>
+        <v>180</v>
+      </c>
+      <c r="C57" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D57" t="b">
         <v>0</v>
@@ -8208,28 +8212,28 @@
         <v>45387</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J57" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K57">
         <v>1035867</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M57" s="21">
         <v>45560</v>
       </c>
       <c r="N57" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O57" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P57" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q57">
         <v>22.78</v>
@@ -8245,7 +8249,7 @@
         <v>0</v>
       </c>
       <c r="AG57" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AH57">
         <f t="shared" si="0"/>
@@ -8258,39 +8262,39 @@
         <v>0</v>
       </c>
       <c r="AP57" t="s">
+        <v>72</v>
+      </c>
+      <c r="AR57" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AT57" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU57" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW57" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX57" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY57" t="s">
         <v>73</v>
       </c>
-      <c r="AR57" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT57" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU57" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW57" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX57" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY57" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ57" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="58" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B58" t="s">
-        <v>181</v>
-      </c>
-      <c r="C58">
-        <v>1</v>
+        <v>180</v>
+      </c>
+      <c r="C58" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D58" t="b">
         <v>0</v>
@@ -8302,28 +8306,28 @@
         <v>45387</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J58" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K58">
         <v>1035964</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M58" s="21">
         <v>45560</v>
       </c>
       <c r="N58" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O58" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P58" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q58">
         <v>2.15</v>
@@ -8339,7 +8343,7 @@
         <v>0</v>
       </c>
       <c r="AG58" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AH58">
         <f t="shared" si="0"/>
@@ -8352,39 +8356,39 @@
         <v>0</v>
       </c>
       <c r="AP58" t="s">
+        <v>72</v>
+      </c>
+      <c r="AR58" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AT58" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU58" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW58" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX58" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY58" t="s">
         <v>73</v>
       </c>
-      <c r="AR58" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT58" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU58" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW58" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX58" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY58" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ58" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="59" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B59" t="s">
-        <v>181</v>
-      </c>
-      <c r="C59">
-        <v>1</v>
+        <v>180</v>
+      </c>
+      <c r="C59" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D59" t="b">
         <v>0</v>
@@ -8396,28 +8400,28 @@
         <v>45387</v>
       </c>
       <c r="I59" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J59" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K59">
         <v>1036019</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M59" s="21">
         <v>45560</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O59" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P59" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q59">
         <v>69.650000000000006</v>
@@ -8433,7 +8437,7 @@
         <v>0</v>
       </c>
       <c r="AG59" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AH59">
         <f t="shared" si="0"/>
@@ -8446,39 +8450,39 @@
         <v>0</v>
       </c>
       <c r="AP59" t="s">
+        <v>72</v>
+      </c>
+      <c r="AR59" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AT59" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU59" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW59" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX59" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY59" t="s">
         <v>73</v>
       </c>
-      <c r="AR59" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT59" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU59" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW59" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX59" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY59" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ59" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="60" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B60" t="s">
-        <v>181</v>
-      </c>
-      <c r="C60">
-        <v>1</v>
+        <v>180</v>
+      </c>
+      <c r="C60" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D60" t="b">
         <v>0</v>
@@ -8490,28 +8494,28 @@
         <v>45387</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J60" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K60">
         <v>1036173</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M60" s="21">
         <v>45560</v>
       </c>
       <c r="N60" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O60" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P60" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q60">
         <v>156.4</v>
@@ -8527,7 +8531,7 @@
         <v>0</v>
       </c>
       <c r="AG60" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AH60">
         <f t="shared" si="0"/>
@@ -8540,39 +8544,39 @@
         <v>0</v>
       </c>
       <c r="AP60" t="s">
+        <v>72</v>
+      </c>
+      <c r="AR60" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AT60" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU60" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW60" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX60" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY60" t="s">
         <v>73</v>
       </c>
-      <c r="AR60" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT60" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU60" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW60" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX60" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY60" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ60" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="61" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B61" t="s">
-        <v>181</v>
-      </c>
-      <c r="C61">
-        <v>1</v>
+        <v>180</v>
+      </c>
+      <c r="C61" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D61" t="b">
         <v>0</v>
@@ -8584,28 +8588,28 @@
         <v>45387</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J61" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K61">
         <v>1036183</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M61" s="21">
         <v>45560</v>
       </c>
       <c r="N61" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O61" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P61" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q61">
         <v>1.41</v>
@@ -8621,7 +8625,7 @@
         <v>0</v>
       </c>
       <c r="AG61" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AH61">
         <f t="shared" si="0"/>
@@ -8634,39 +8638,39 @@
         <v>0</v>
       </c>
       <c r="AP61" t="s">
+        <v>72</v>
+      </c>
+      <c r="AR61" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AT61" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU61" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW61" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX61" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY61" t="s">
         <v>73</v>
       </c>
-      <c r="AR61" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT61" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU61" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW61" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX61" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY61" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ61" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="62" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B62" t="s">
-        <v>181</v>
-      </c>
-      <c r="C62">
-        <v>1</v>
+        <v>180</v>
+      </c>
+      <c r="C62" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D62" t="b">
         <v>0</v>
@@ -8678,28 +8682,28 @@
         <v>45387</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J62" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K62">
         <v>1036318</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M62" s="21">
         <v>45560</v>
       </c>
       <c r="N62" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O62" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P62" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q62">
         <v>151.12</v>
@@ -8715,7 +8719,7 @@
         <v>0</v>
       </c>
       <c r="AG62" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AH62">
         <f t="shared" si="0"/>
@@ -8728,39 +8732,39 @@
         <v>0</v>
       </c>
       <c r="AP62" t="s">
+        <v>72</v>
+      </c>
+      <c r="AR62" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AT62" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU62" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW62" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX62" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY62" t="s">
         <v>73</v>
       </c>
-      <c r="AR62" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT62" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU62" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW62" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX62" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY62" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ62" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="63" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B63" t="s">
-        <v>181</v>
-      </c>
-      <c r="C63">
-        <v>1</v>
+        <v>180</v>
+      </c>
+      <c r="C63" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D63" t="b">
         <v>0</v>
@@ -8772,28 +8776,28 @@
         <v>45387</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K63">
         <v>1036385</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M63" s="21">
         <v>45560</v>
       </c>
       <c r="N63" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O63" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P63" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q63">
         <v>1.41</v>
@@ -8809,7 +8813,7 @@
         <v>0</v>
       </c>
       <c r="AG63" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AH63">
         <f t="shared" si="0"/>
@@ -8822,39 +8826,39 @@
         <v>0</v>
       </c>
       <c r="AP63" t="s">
+        <v>72</v>
+      </c>
+      <c r="AR63" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AT63" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU63" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW63" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX63" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY63" t="s">
         <v>73</v>
       </c>
-      <c r="AR63" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT63" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU63" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW63" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX63" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY63" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ63" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="64" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B64" t="s">
-        <v>181</v>
-      </c>
-      <c r="C64">
-        <v>1</v>
+        <v>180</v>
+      </c>
+      <c r="C64" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D64" t="b">
         <v>0</v>
@@ -8866,28 +8870,28 @@
         <v>45387</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J64" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K64">
         <v>1036472</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M64" s="21">
         <v>45560</v>
       </c>
       <c r="N64" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O64" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P64" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q64">
         <v>10.16</v>
@@ -8903,7 +8907,7 @@
         <v>0</v>
       </c>
       <c r="AG64" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AH64">
         <f t="shared" si="0"/>
@@ -8916,39 +8920,39 @@
         <v>0</v>
       </c>
       <c r="AP64" t="s">
+        <v>72</v>
+      </c>
+      <c r="AR64" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AT64" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU64" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW64" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX64" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY64" t="s">
         <v>73</v>
       </c>
-      <c r="AR64" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT64" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU64" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW64" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX64" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY64" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ64" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="65" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B65" t="s">
-        <v>181</v>
-      </c>
-      <c r="C65">
-        <v>1</v>
+        <v>180</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D65" t="b">
         <v>0</v>
@@ -8960,28 +8964,28 @@
         <v>45387</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J65" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K65">
         <v>1037119</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M65" s="21">
         <v>45560</v>
       </c>
       <c r="N65" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O65" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P65" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q65">
         <v>28.43</v>
@@ -8997,7 +9001,7 @@
         <v>0</v>
       </c>
       <c r="AG65" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AH65">
         <f t="shared" ref="AH65:AH78" si="3">Q65+R65+U65+X65+Y65</f>
@@ -9010,39 +9014,39 @@
         <v>0</v>
       </c>
       <c r="AP65" t="s">
+        <v>72</v>
+      </c>
+      <c r="AR65" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AT65" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU65" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW65" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX65" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY65" t="s">
         <v>73</v>
       </c>
-      <c r="AR65" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT65" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU65" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW65" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX65" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY65" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ65" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="66" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B66" t="s">
-        <v>181</v>
-      </c>
-      <c r="C66">
-        <v>1</v>
+        <v>180</v>
+      </c>
+      <c r="C66" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D66" t="b">
         <v>0</v>
@@ -9054,28 +9058,28 @@
         <v>45387</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J66" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K66">
         <v>1036473</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M66" s="21">
         <v>45560</v>
       </c>
       <c r="N66" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O66" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P66" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q66">
         <v>3.61</v>
@@ -9091,7 +9095,7 @@
         <v>0</v>
       </c>
       <c r="AG66" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AH66">
         <f t="shared" si="3"/>
@@ -9104,39 +9108,39 @@
         <v>0</v>
       </c>
       <c r="AP66" t="s">
+        <v>72</v>
+      </c>
+      <c r="AR66" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AT66" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU66" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW66" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX66" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY66" t="s">
         <v>73</v>
       </c>
-      <c r="AR66" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT66" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU66" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW66" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX66" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY66" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ66" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="67" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B67" t="s">
-        <v>181</v>
-      </c>
-      <c r="C67">
-        <v>1</v>
+        <v>180</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D67" t="b">
         <v>0</v>
@@ -9148,28 +9152,28 @@
         <v>45387</v>
       </c>
       <c r="I67" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J67" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K67">
         <v>1036539</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M67" s="21">
         <v>45560</v>
       </c>
       <c r="N67" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O67" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P67" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q67">
         <v>1.41</v>
@@ -9185,7 +9189,7 @@
         <v>0</v>
       </c>
       <c r="AG67" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AH67">
         <f t="shared" si="3"/>
@@ -9198,39 +9202,39 @@
         <v>0</v>
       </c>
       <c r="AP67" t="s">
+        <v>72</v>
+      </c>
+      <c r="AR67" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AT67" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU67" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW67" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX67" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY67" t="s">
         <v>73</v>
       </c>
-      <c r="AR67" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT67" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU67" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW67" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX67" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY67" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ67" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="68" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B68" t="s">
-        <v>181</v>
-      </c>
-      <c r="C68">
-        <v>1</v>
+        <v>180</v>
+      </c>
+      <c r="C68" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D68" t="b">
         <v>0</v>
@@ -9242,28 +9246,28 @@
         <v>45387</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J68" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K68">
         <v>1036635</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M68" s="21">
         <v>45560</v>
       </c>
       <c r="N68" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O68" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P68" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q68">
         <v>18.93</v>
@@ -9279,7 +9283,7 @@
         <v>0</v>
       </c>
       <c r="AG68" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AH68">
         <f t="shared" si="3"/>
@@ -9292,39 +9296,39 @@
         <v>0</v>
       </c>
       <c r="AP68" t="s">
+        <v>72</v>
+      </c>
+      <c r="AR68" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AT68" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU68" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW68" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX68" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY68" t="s">
         <v>73</v>
       </c>
-      <c r="AR68" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT68" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU68" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW68" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX68" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY68" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ68" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="69" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B69" t="s">
-        <v>181</v>
-      </c>
-      <c r="C69">
-        <v>1</v>
+        <v>180</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D69" t="b">
         <v>0</v>
@@ -9336,28 +9340,28 @@
         <v>45387</v>
       </c>
       <c r="I69" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J69" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K69">
         <v>1036826</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M69" s="21">
         <v>45560</v>
       </c>
       <c r="N69" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O69" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P69" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q69">
         <v>85.08</v>
@@ -9373,7 +9377,7 @@
         <v>0</v>
       </c>
       <c r="AG69" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AH69">
         <f t="shared" si="3"/>
@@ -9386,39 +9390,39 @@
         <v>0</v>
       </c>
       <c r="AP69" t="s">
+        <v>72</v>
+      </c>
+      <c r="AR69" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AT69" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU69" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW69" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX69" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY69" t="s">
         <v>73</v>
       </c>
-      <c r="AR69" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT69" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU69" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW69" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX69" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY69" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ69" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="70" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B70" t="s">
-        <v>181</v>
-      </c>
-      <c r="C70">
-        <v>1</v>
+        <v>180</v>
+      </c>
+      <c r="C70" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D70" t="b">
         <v>0</v>
@@ -9430,28 +9434,28 @@
         <v>45387</v>
       </c>
       <c r="I70" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J70" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K70">
         <v>1036937</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M70" s="21">
         <v>45560</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O70" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P70" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q70">
         <v>45.35</v>
@@ -9467,7 +9471,7 @@
         <v>0</v>
       </c>
       <c r="AG70" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AH70">
         <f t="shared" si="3"/>
@@ -9480,39 +9484,39 @@
         <v>0</v>
       </c>
       <c r="AP70" t="s">
+        <v>72</v>
+      </c>
+      <c r="AR70" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AT70" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU70" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW70" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX70" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY70" t="s">
         <v>73</v>
       </c>
-      <c r="AR70" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT70" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU70" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW70" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX70" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY70" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ70" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="71" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B71" t="s">
-        <v>181</v>
-      </c>
-      <c r="C71">
-        <v>1</v>
+        <v>180</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D71" t="b">
         <v>0</v>
@@ -9524,28 +9528,28 @@
         <v>45387</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="K71">
         <v>1036938</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="M71" s="21">
         <v>45560</v>
       </c>
       <c r="N71" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O71" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P71" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q71">
         <v>1.41</v>
@@ -9561,7 +9565,7 @@
         <v>0</v>
       </c>
       <c r="AG71" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AH71">
         <f t="shared" si="3"/>
@@ -9574,39 +9578,39 @@
         <v>0</v>
       </c>
       <c r="AP71" t="s">
+        <v>72</v>
+      </c>
+      <c r="AR71" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AT71" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU71" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW71" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX71" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY71" t="s">
         <v>73</v>
       </c>
-      <c r="AR71" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT71" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU71" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW71" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX71" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY71" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ71" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="72" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B72" t="s">
         <v>183</v>
       </c>
-      <c r="B72" t="s">
-        <v>184</v>
-      </c>
-      <c r="C72">
-        <v>1</v>
+      <c r="C72" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D72" t="b">
         <v>0</v>
@@ -9618,28 +9622,28 @@
         <v>45387</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J72" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K72">
         <v>6634435</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="M72" s="21">
         <v>45594</v>
       </c>
       <c r="N72" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O72" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P72" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q72">
         <v>59.23</v>
@@ -9655,7 +9659,7 @@
         <v>0</v>
       </c>
       <c r="AG72" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AH72">
         <f t="shared" si="3"/>
@@ -9668,39 +9672,39 @@
         <v>0</v>
       </c>
       <c r="AP72" t="s">
+        <v>72</v>
+      </c>
+      <c r="AR72" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AT72" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU72" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW72" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX72" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY72" t="s">
         <v>73</v>
       </c>
-      <c r="AR72" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT72" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU72" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW72" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX72" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY72" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ72" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="73" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B73" t="s">
         <v>183</v>
       </c>
-      <c r="B73" t="s">
-        <v>184</v>
-      </c>
-      <c r="C73">
-        <v>1</v>
+      <c r="C73" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D73" t="b">
         <v>0</v>
@@ -9712,28 +9716,28 @@
         <v>45387</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J73" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K73">
         <v>6634344</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="M73" s="21">
         <v>45594</v>
       </c>
       <c r="N73" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O73" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P73" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q73">
         <v>1.67</v>
@@ -9749,7 +9753,7 @@
         <v>0</v>
       </c>
       <c r="AG73" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AH73">
         <f t="shared" si="3"/>
@@ -9762,39 +9766,39 @@
         <v>0</v>
       </c>
       <c r="AP73" t="s">
+        <v>72</v>
+      </c>
+      <c r="AR73" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AT73" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU73" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW73" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX73" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY73" t="s">
         <v>73</v>
       </c>
-      <c r="AR73" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT73" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU73" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW73" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX73" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY73" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ73" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="74" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B74" t="s">
         <v>188</v>
       </c>
-      <c r="B74" t="s">
-        <v>189</v>
-      </c>
-      <c r="C74">
-        <v>1</v>
+      <c r="C74" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D74" t="b">
         <v>0</v>
@@ -9806,28 +9810,28 @@
         <v>45388</v>
       </c>
       <c r="I74" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J74" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="J74" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="K74">
         <v>21117954</v>
       </c>
       <c r="L74" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="M74" s="21">
         <v>45566</v>
       </c>
       <c r="N74" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O74" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P74" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q74">
         <v>0</v>
@@ -9843,7 +9847,7 @@
         <v>0.97</v>
       </c>
       <c r="AG74" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AH74">
         <f t="shared" si="3"/>
@@ -9856,39 +9860,39 @@
         <v>0</v>
       </c>
       <c r="AP74" t="s">
+        <v>72</v>
+      </c>
+      <c r="AR74" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AT74" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU74" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW74" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX74" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY74" t="s">
         <v>73</v>
       </c>
-      <c r="AR74" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT74" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU74" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW74" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX74" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY74" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ74" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="75" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B75" t="s">
         <v>188</v>
       </c>
-      <c r="B75" t="s">
-        <v>189</v>
-      </c>
-      <c r="C75">
-        <v>1</v>
+      <c r="C75" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D75" t="b">
         <v>0</v>
@@ -9900,28 +9904,28 @@
         <v>45388</v>
       </c>
       <c r="I75" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J75" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="J75" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="K75">
         <v>21117955</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="M75" s="21">
         <v>45566</v>
       </c>
       <c r="N75" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O75" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P75" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q75">
         <v>0</v>
@@ -9937,7 +9941,7 @@
         <v>2.3199999999999998</v>
       </c>
       <c r="AG75" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AH75">
         <f t="shared" si="3"/>
@@ -9950,39 +9954,39 @@
         <v>0</v>
       </c>
       <c r="AP75" t="s">
+        <v>72</v>
+      </c>
+      <c r="AR75" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AT75" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU75" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW75" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX75" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY75" t="s">
         <v>73</v>
       </c>
-      <c r="AR75" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT75" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU75" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW75" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX75" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY75" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ75" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="76" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B76" t="s">
         <v>188</v>
       </c>
-      <c r="B76" t="s">
-        <v>189</v>
-      </c>
-      <c r="C76">
-        <v>1</v>
+      <c r="C76" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D76" t="b">
         <v>0</v>
@@ -9994,28 +9998,28 @@
         <v>45388</v>
       </c>
       <c r="I76" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J76" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="J76" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="K76">
         <v>21117958</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="M76" s="21">
         <v>45566</v>
       </c>
       <c r="N76" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O76" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P76" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q76">
         <v>0</v>
@@ -10031,7 +10035,7 @@
         <v>7.47</v>
       </c>
       <c r="AG76" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AH76">
         <f t="shared" si="3"/>
@@ -10044,39 +10048,39 @@
         <v>0</v>
       </c>
       <c r="AP76" t="s">
+        <v>72</v>
+      </c>
+      <c r="AR76" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AT76" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU76" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW76" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX76" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY76" t="s">
         <v>73</v>
       </c>
-      <c r="AR76" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT76" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU76" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW76" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX76" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY76" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ76" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="77" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B77" t="s">
         <v>188</v>
       </c>
-      <c r="B77" t="s">
-        <v>189</v>
-      </c>
-      <c r="C77">
-        <v>1</v>
+      <c r="C77" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D77" t="b">
         <v>0</v>
@@ -10088,28 +10092,28 @@
         <v>45388</v>
       </c>
       <c r="I77" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J77" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="J77" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="K77">
         <v>21117966</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="M77" s="21">
         <v>45566</v>
       </c>
       <c r="N77" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O77" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P77" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q77">
         <v>0</v>
@@ -10125,7 +10129,7 @@
         <v>1.07</v>
       </c>
       <c r="AG77" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AH77">
         <f t="shared" si="3"/>
@@ -10138,39 +10142,39 @@
         <v>0</v>
       </c>
       <c r="AP77" t="s">
+        <v>72</v>
+      </c>
+      <c r="AR77" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AT77" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU77" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW77" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX77" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY77" t="s">
         <v>73</v>
       </c>
-      <c r="AR77" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT77" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU77" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW77" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX77" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY77" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ77" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="78" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B78" t="s">
         <v>188</v>
       </c>
-      <c r="B78" t="s">
-        <v>189</v>
-      </c>
-      <c r="C78">
-        <v>1</v>
+      <c r="C78" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="D78" t="b">
         <v>0</v>
@@ -10182,28 +10186,28 @@
         <v>45388</v>
       </c>
       <c r="I78" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J78" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="J78" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="K78">
         <v>21117947</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="M78" s="21">
         <v>45566</v>
       </c>
       <c r="N78" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O78" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P78" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="Q78">
         <v>0</v>
@@ -10219,7 +10223,7 @@
         <v>0.93</v>
       </c>
       <c r="AG78" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="AH78">
         <f t="shared" si="3"/>
@@ -10232,39 +10236,39 @@
         <v>0</v>
       </c>
       <c r="AP78" t="s">
+        <v>72</v>
+      </c>
+      <c r="AR78" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AT78" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU78" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW78" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX78" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY78" t="s">
         <v>73</v>
       </c>
-      <c r="AR78" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AT78" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="AU78" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW78" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX78" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY78" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ78" s="15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="79" spans="1:61" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="12" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B79" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="C79" s="14">
-        <v>1</v>
+        <v>171</v>
+      </c>
+      <c r="C79" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="D79" s="14" t="b">
         <v>0</v>
@@ -10278,28 +10282,28 @@
         <v>45412</v>
       </c>
       <c r="I79" s="18" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J79" s="12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K79" s="14">
         <v>209</v>
       </c>
       <c r="L79" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="M79" s="21">
         <v>45647</v>
       </c>
       <c r="N79" s="12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="O79" s="14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P79" s="19" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="Q79" s="14">
         <v>0</v>
@@ -10319,44 +10323,44 @@
       <c r="AR79" s="12"/>
       <c r="AS79" s="3"/>
       <c r="AT79" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="AU79" s="14" t="s">
         <v>65</v>
-      </c>
-      <c r="AU79" s="14" t="s">
-        <v>66</v>
       </c>
       <c r="AV79" s="14">
         <v>305</v>
       </c>
       <c r="AW79" s="12" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AX79" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY79" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="AY79" s="14" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ79" s="12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="BA79" s="12"/>
       <c r="BI79" s="12"/>
     </row>
     <row r="80" spans="1:61" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="B80" s="14" t="s">
         <v>207</v>
       </c>
-      <c r="B80" s="14" t="s">
-        <v>208</v>
-      </c>
-      <c r="C80" s="14">
-        <v>3</v>
+      <c r="C80" s="9" t="s">
+        <v>214</v>
       </c>
       <c r="D80" s="14" t="b">
         <v>0</v>
       </c>
       <c r="E80" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F80" s="13"/>
       <c r="G80" s="22">
@@ -10366,28 +10370,28 @@
         <v>45412</v>
       </c>
       <c r="I80" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="J80" s="12" t="s">
         <v>65</v>
-      </c>
-      <c r="J80" s="12" t="s">
-        <v>66</v>
       </c>
       <c r="K80" s="14">
         <v>78787887</v>
       </c>
       <c r="L80" s="12" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M80" s="22">
         <v>45647</v>
       </c>
       <c r="N80" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O80" s="14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P80" s="19" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q80" s="14">
         <v>100</v>
@@ -10409,42 +10413,42 @@
       <c r="AT80" s="12"/>
       <c r="AV80" s="12"/>
       <c r="AW80" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY80" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="AY80" s="14" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ80" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="BA80" s="12" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="BE80" s="20" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="BF80" s="12" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="BI80" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="81" spans="1:61" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="B81" s="14" t="s">
         <v>209</v>
       </c>
-      <c r="B81" s="14" t="s">
-        <v>210</v>
-      </c>
-      <c r="C81" s="14">
-        <v>3</v>
+      <c r="C81" s="9" t="s">
+        <v>214</v>
       </c>
       <c r="D81" s="14" t="b">
         <v>0</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F81" s="13"/>
       <c r="G81" s="22">
@@ -10454,28 +10458,28 @@
         <v>45412</v>
       </c>
       <c r="I81" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="J81" s="12" t="s">
         <v>65</v>
-      </c>
-      <c r="J81" s="12" t="s">
-        <v>66</v>
       </c>
       <c r="K81" s="14">
         <v>232323</v>
       </c>
       <c r="L81" s="12" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M81" s="22">
         <v>45647</v>
       </c>
       <c r="N81" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O81" s="14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P81" s="19" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q81" s="14">
         <v>100</v>
@@ -10497,40 +10501,40 @@
       <c r="AT81" s="12"/>
       <c r="AV81" s="12"/>
       <c r="AY81" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AZ81" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="BA81" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="BE81" s="20" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="BF81" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="BG81" s="20"/>
       <c r="BI81" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="82" spans="1:61" s="14" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="B82" s="14" t="s">
         <v>211</v>
       </c>
-      <c r="B82" s="14" t="s">
-        <v>212</v>
-      </c>
-      <c r="C82" s="14">
-        <v>3</v>
+      <c r="C82" s="9" t="s">
+        <v>214</v>
       </c>
       <c r="D82" s="14" t="b">
         <v>0</v>
       </c>
       <c r="E82" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F82" s="13"/>
       <c r="G82" s="22">
@@ -10540,28 +10544,28 @@
         <v>45412</v>
       </c>
       <c r="I82" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="J82" s="12" t="s">
         <v>65</v>
-      </c>
-      <c r="J82" s="12" t="s">
-        <v>66</v>
       </c>
       <c r="K82" s="14">
         <v>65656</v>
       </c>
       <c r="L82" s="12" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M82" s="22">
         <v>45647</v>
       </c>
       <c r="N82" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O82" s="14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P82" s="19" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="Q82" s="14">
         <v>100</v>
@@ -10583,43 +10587,43 @@
       <c r="AT82" s="12"/>
       <c r="AV82" s="12"/>
       <c r="AW82" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY82" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="AY82" s="14" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ82" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="BA82" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="BE82" s="20" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="BF82" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="BG82" s="20"/>
       <c r="BI82" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="83" spans="1:61" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="B83" t="s">
         <v>213</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C83" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="C83" s="10">
-        <v>3</v>
-      </c>
       <c r="D83" s="10" t="b">
         <v>0</v>
       </c>
       <c r="E83" s="12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F83" s="12"/>
       <c r="G83" s="22">
@@ -10629,28 +10633,28 @@
         <v>45387</v>
       </c>
       <c r="I83" s="12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J83" s="12" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="K83" s="10">
         <v>9999999</v>
       </c>
       <c r="L83" s="12" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="M83" s="22">
         <v>45721</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="O83" s="14" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P83" s="14" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Q83" s="10">
         <v>300</v>
@@ -10666,7 +10670,7 @@
         <v>0</v>
       </c>
       <c r="AG83" s="12" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AH83" s="10">
         <f t="shared" ref="AH83" si="5">Q83+R83+U83+X83+Y83</f>
@@ -10679,56 +10683,55 @@
         <v>3</v>
       </c>
       <c r="AP83" s="10" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="AQ83" s="10">
         <v>13000</v>
       </c>
       <c r="AR83" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AS83" s="11">
         <v>45387</v>
       </c>
       <c r="AT83" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="AU83" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW83" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AX83" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="AY83" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="AU83" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW83" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="AX83" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="AY83" s="10" t="s">
-        <v>74</v>
-      </c>
       <c r="AZ83" s="12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="BA83" s="15" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="BB83"/>
       <c r="BC83"/>
       <c r="BD83"/>
       <c r="BE83" s="20" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="BF83" s="15" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="BG83"/>
       <c r="BH83"/>
       <c r="BI83" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="85" spans="1:61" x14ac:dyDescent="0.25">
       <c r="B85" s="1"/>
-      <c r="C85" s="1"/>
       <c r="D85" s="1"/>
       <c r="G85" s="1"/>
       <c r="H85" s="1"/>
